--- a/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/correctionProfile/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
